--- a/bizconfig/static-xlsx/moba/pixel_moba/unit.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/unit.xlsx
@@ -4,25 +4,96 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="600" autoFilterDateGrouping="true"/>
   </bookViews>
   <sheets>
-    <sheet name="Unit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Unit" sheetId="1" r:id="rId1" state="visible"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>buff_npc</t>
+  </si>
+  <si>
+    <t>增益怪</t>
+  </si>
+  <si>
+    <t>monster</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>wolf</t>
+  </si>
+  <si>
+    <t>狼</t>
+  </si>
+  <si>
+    <t>bird</t>
+  </si>
+  <si>
+    <t>鸟</t>
+  </si>
+  <si>
+    <t>golem</t>
+  </si>
+  <si>
+    <t>石头人</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>河道Boss</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>is_ranged</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>notnull</t>
+  </si>
+  <si>
+    <t>!s!c</t>
+  </si>
+  <si>
+    <t>是否远程攻击</t>
+  </si>
+  <si>
+    <t>attack_projectile_speed</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>远程平A弹道速度</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -47,12 +118,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -125,7 +196,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -408,9 +479,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AL10"/>
@@ -597,15 +668,11 @@
           <t>hit_rate</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>slow_resist</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>tenacity</t>
-        </is>
+      <c r="AK1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2">
@@ -789,15 +856,11 @@
           <t>float</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
+      <c r="AK2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -981,15 +1044,11 @@
           <t>notnull</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>notnull</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>notnull</t>
-        </is>
+      <c r="AK3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1173,15 +1232,11 @@
           <t>!s!c</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>!s!c</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>!s!c</t>
-        </is>
+      <c r="AK4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1365,15 +1420,11 @@
           <t>命中率(0-1)</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>减速抗性(0-1)</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>韧性(减控0-1)</t>
-        </is>
+      <c r="AK5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1495,10 +1546,10 @@
       <c r="AJ6" t="n">
         <v>1</v>
       </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
+      <c r="AK6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL6">
         <v>0</v>
       </c>
     </row>
@@ -1621,11 +1672,11 @@
       <c r="AJ7" t="n">
         <v>1</v>
       </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
+      <c r="AK7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL7">
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1747,11 +1798,11 @@
       <c r="AJ8" t="n">
         <v>1</v>
       </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
+      <c r="AK8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL8">
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -1871,10 +1922,10 @@
       <c r="AJ9" t="n">
         <v>1</v>
       </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="AK9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL9">
         <v>0</v>
       </c>
     </row>
@@ -1993,10 +2044,590 @@
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
+      <c r="AK10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>4001</v>
+      </c>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>50000</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>50</v>
+      </c>
+      <c r="I11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>300</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>20</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+      <c r="R11">
+        <v>10</v>
+      </c>
+      <c r="S11">
+        <v>0.3</v>
+      </c>
+      <c r="T11">
+        <v>0.4</v>
+      </c>
+      <c r="U11">
+        <v>0.7</v>
+      </c>
+      <c r="V11">
+        <v>30</v>
+      </c>
+      <c r="W11">
+        <v>80</v>
+      </c>
+      <c r="X11">
+        <v>12</v>
+      </c>
+      <c r="Y11">
+        <v>128</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>2</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4002</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>50000</v>
+      </c>
+      <c r="G12">
+        <v>15</v>
+      </c>
+      <c r="H12">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12">
+        <v>150</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>15</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>6</v>
+      </c>
+      <c r="R12">
+        <v>6</v>
+      </c>
+      <c r="S12">
+        <v>0.25</v>
+      </c>
+      <c r="T12">
+        <v>0.3</v>
+      </c>
+      <c r="U12">
+        <v>0.55</v>
+      </c>
+      <c r="V12">
+        <v>25</v>
+      </c>
+      <c r="W12">
+        <v>120</v>
+      </c>
+      <c r="X12">
+        <v>10</v>
+      </c>
+      <c r="Y12">
+        <v>128</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>2</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>4003</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>50000</v>
+      </c>
+      <c r="G13">
+        <v>15</v>
+      </c>
+      <c r="H13">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" t="s">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>120</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>12</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>4</v>
+      </c>
+      <c r="R13">
+        <v>4</v>
+      </c>
+      <c r="S13">
+        <v>0.2</v>
+      </c>
+      <c r="T13">
+        <v>0.3</v>
+      </c>
+      <c r="U13">
+        <v>0.5</v>
+      </c>
+      <c r="V13">
+        <v>60</v>
+      </c>
+      <c r="W13">
+        <v>100</v>
+      </c>
+      <c r="X13">
+        <v>8</v>
+      </c>
+      <c r="Y13">
+        <v>160</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>2</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>4004</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>50000</v>
+      </c>
+      <c r="G14">
+        <v>40</v>
+      </c>
+      <c r="H14">
+        <v>70</v>
+      </c>
+      <c r="I14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <v>500</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>30</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>20</v>
+      </c>
+      <c r="R14">
+        <v>15</v>
+      </c>
+      <c r="S14">
+        <v>0.4</v>
+      </c>
+      <c r="T14">
+        <v>0.5</v>
+      </c>
+      <c r="U14">
+        <v>0.9</v>
+      </c>
+      <c r="V14">
+        <v>30</v>
+      </c>
+      <c r="W14">
+        <v>60</v>
+      </c>
+      <c r="X14">
+        <v>16</v>
+      </c>
+      <c r="Y14">
+        <v>128</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>2</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>4005</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>120000</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <v>150</v>
+      </c>
+      <c r="I15" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>800</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>40</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>30</v>
+      </c>
+      <c r="R15">
+        <v>25</v>
+      </c>
+      <c r="S15">
+        <v>0.5</v>
+      </c>
+      <c r="T15">
+        <v>0.6</v>
+      </c>
+      <c r="U15">
+        <v>1.1</v>
+      </c>
+      <c r="V15">
+        <v>40</v>
+      </c>
+      <c r="W15">
+        <v>50</v>
+      </c>
+      <c r="X15">
+        <v>20</v>
+      </c>
+      <c r="Y15">
+        <v>192</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>2</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL15">
         <v>0</v>
       </c>
     </row>
